--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105360_W4.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105360_W4.xlsx
@@ -570,67 +570,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.2142</v>
+        <v>8.2713</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7665</v>
+        <v>6.9302</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4477</v>
+        <v>1.3411</v>
       </c>
       <c r="G2" t="n">
-        <v>7.0444</v>
+        <v>7.1277</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4626</v>
+        <v>3.4766</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5818</v>
+        <v>3.6511</v>
       </c>
       <c r="J2" t="n">
-        <v>5.5501</v>
+        <v>5.7725</v>
       </c>
       <c r="K2" t="n">
-        <v>2.6116</v>
+        <v>2.721</v>
       </c>
       <c r="L2" t="n">
-        <v>2.9385</v>
+        <v>3.0515</v>
       </c>
       <c r="M2" t="n">
-        <v>1.4943</v>
+        <v>1.3552</v>
       </c>
       <c r="N2" t="n">
-        <v>0.851</v>
+        <v>0.7556</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6433</v>
+        <v>0.5996</v>
       </c>
       <c r="P2" t="n">
-        <v>1.399</v>
+        <v>1.377</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.399</v>
+        <v>1.377</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3045</v>
+        <v>0.3077</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6828</v>
+        <v>0.6168</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3783</v>
+        <v>-0.309</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.5337</v>
+        <v>-0.541</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5337</v>
+        <v>0.541</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0673</v>
+        <v>-1.082</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -653,64 +653,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.241</v>
+        <v>7.2562</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2021</v>
+        <v>5.3215</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0388</v>
+        <v>1.9347</v>
       </c>
       <c r="G3" t="n">
-        <v>5.9209</v>
+        <v>5.9134</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0476</v>
+        <v>2.0096</v>
       </c>
       <c r="I3" t="n">
-        <v>3.8734</v>
+        <v>3.9038</v>
       </c>
       <c r="J3" t="n">
-        <v>5.9327</v>
+        <v>6.0663</v>
       </c>
       <c r="K3" t="n">
-        <v>2.7027</v>
+        <v>2.7622</v>
       </c>
       <c r="L3" t="n">
-        <v>3.23</v>
+        <v>3.3042</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0118</v>
+        <v>-0.1529</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6551</v>
+        <v>-0.7524999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6433</v>
+        <v>0.5996</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.1658</v>
+        <v>-1.1475</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3317</v>
+        <v>-2.295</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1658</v>
+        <v>1.1475</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4186</v>
+        <v>1.4083</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5338000000000001</v>
+        <v>0.4681</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8848</v>
+        <v>0.9401</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0673</v>
+        <v>1.082</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0673</v>
+        <v>1.082</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -736,67 +736,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5528</v>
+        <v>4.4924</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3924</v>
+        <v>3.4875</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1603</v>
+        <v>1.0048</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1581</v>
+        <v>3.1163</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0192</v>
+        <v>1.0313</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1389</v>
+        <v>2.0851</v>
       </c>
       <c r="J4" t="n">
-        <v>1.351</v>
+        <v>1.5201</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0063</v>
+        <v>0.1493</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3573</v>
+        <v>1.3709</v>
       </c>
       <c r="M4" t="n">
-        <v>1.8071</v>
+        <v>1.5962</v>
       </c>
       <c r="N4" t="n">
-        <v>1.0255</v>
+        <v>0.882</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7816</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>1.399</v>
+        <v>1.377</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.399</v>
+        <v>1.377</v>
       </c>
       <c r="S4" t="n">
-        <v>0.133</v>
+        <v>0.15</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9741</v>
+        <v>0.8854</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8411</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1373</v>
+        <v>-0.1509</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0673</v>
+        <v>1.082</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2046</v>
+        <v>-1.2329</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -819,67 +819,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2828</v>
+        <v>4.3695</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0877</v>
+        <v>4.2846</v>
       </c>
       <c r="F5" t="n">
-        <v>0.195</v>
+        <v>0.0849</v>
       </c>
       <c r="G5" t="n">
-        <v>5.6574</v>
+        <v>5.7188</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8782</v>
+        <v>0.8249</v>
       </c>
       <c r="I5" t="n">
-        <v>4.7792</v>
+        <v>4.8939</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6937</v>
+        <v>4.9223</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3594</v>
+        <v>0.4192</v>
       </c>
       <c r="L5" t="n">
-        <v>4.3343</v>
+        <v>4.5031</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9637</v>
+        <v>0.7966</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5189</v>
+        <v>0.4057</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4449</v>
+        <v>0.3908</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4663</v>
+        <v>-0.459</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1658</v>
+        <v>-1.1475</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6995</v>
+        <v>0.6885</v>
       </c>
       <c r="S5" t="n">
-        <v>0.159</v>
+        <v>0.1917</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5599</v>
+        <v>0.5098</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4008</v>
+        <v>-0.3182</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0673</v>
+        <v>-1.082</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0673</v>
+        <v>-1.082</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -902,58 +902,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.3197</v>
+        <v>3.3109</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6047</v>
+        <v>0.6878</v>
       </c>
       <c r="F6" t="n">
-        <v>2.715</v>
+        <v>2.6231</v>
       </c>
       <c r="G6" t="n">
-        <v>5.8293</v>
+        <v>5.7558</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2351</v>
+        <v>3.2026</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5941</v>
+        <v>2.5532</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9666</v>
+        <v>4.0389</v>
       </c>
       <c r="K6" t="n">
-        <v>2.7194</v>
+        <v>2.7792</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2472</v>
+        <v>1.2597</v>
       </c>
       <c r="M6" t="n">
-        <v>1.8627</v>
+        <v>1.7169</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5158</v>
+        <v>0.4234</v>
       </c>
       <c r="O6" t="n">
-        <v>1.3469</v>
+        <v>1.2935</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.0985</v>
+        <v>-2.0655</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.4975</v>
+        <v>-3.4424</v>
       </c>
       <c r="R6" t="n">
-        <v>1.399</v>
+        <v>1.377</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.411</v>
+        <v>-0.3794</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1356</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5467</v>
+        <v>-0.4707</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -985,58 +985,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5099</v>
+        <v>2.47</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7472</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7626</v>
+        <v>1.651</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4539</v>
+        <v>1.4086</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2675</v>
+        <v>2.2137</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8136</v>
+        <v>-0.805</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0164</v>
+        <v>0.1358</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4104</v>
+        <v>1.4934</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4268</v>
+        <v>-1.3575</v>
       </c>
       <c r="M7" t="n">
-        <v>1.4703</v>
+        <v>1.2728</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8571</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6132</v>
+        <v>0.5525</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9327</v>
+        <v>0.918</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9327</v>
+        <v>0.918</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1233</v>
+        <v>0.1434</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.6833</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6404</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1068,58 +1068,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4219</v>
+        <v>2.3383</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0243</v>
+        <v>0.0392</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3976</v>
+        <v>2.2991</v>
       </c>
       <c r="G8" t="n">
-        <v>2.0784</v>
+        <v>1.9862</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9799</v>
+        <v>0.9184</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0986</v>
+        <v>1.0678</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3912</v>
+        <v>1.4188</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1345</v>
+        <v>1.1594</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2568</v>
+        <v>0.2594</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6872</v>
+        <v>0.5674</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1546</v>
+        <v>-0.241</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8418</v>
+        <v>0.8084</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2332</v>
+        <v>0.2295</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1658</v>
+        <v>-1.1475</v>
       </c>
       <c r="R8" t="n">
-        <v>1.399</v>
+        <v>1.377</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1102</v>
+        <v>0.1226</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2011</v>
+        <v>-0.2321</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3113</v>
+        <v>0.3547</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1151,67 +1151,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.2599</v>
+        <v>2.2212</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4351</v>
+        <v>1.4893</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8248</v>
+        <v>0.7319</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2352</v>
+        <v>2.2026</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.1552</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3261</v>
+        <v>2.3577</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4199</v>
+        <v>2.4907</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4004</v>
+        <v>0.4092</v>
       </c>
       <c r="L9" t="n">
-        <v>2.0195</v>
+        <v>2.0815</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1847</v>
+        <v>-0.2881</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4913</v>
+        <v>-0.5644</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3066</v>
+        <v>0.2763</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4663</v>
+        <v>-0.459</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1658</v>
+        <v>-1.1475</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6995</v>
+        <v>0.6885</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6284</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>0.181</v>
+        <v>0.146</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4473</v>
+        <v>0.4825</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1373</v>
+        <v>-0.1509</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1373</v>
+        <v>-0.1509</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1234,67 +1234,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3159</v>
+        <v>1.2508</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7036</v>
+        <v>0.7259</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6122</v>
+        <v>0.5248</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3853</v>
+        <v>0.3697</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2988</v>
+        <v>0.3157</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.054</v>
       </c>
       <c r="J10" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.2023</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0487</v>
+        <v>0.054</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1467</v>
+        <v>0.1482</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2872</v>
+        <v>0.1674</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3474</v>
+        <v>0.2617</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0602</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4663</v>
+        <v>0.459</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4663</v>
+        <v>0.459</v>
       </c>
       <c r="S10" t="n">
-        <v>1.7907</v>
+        <v>1.7434</v>
       </c>
       <c r="T10" t="n">
-        <v>1.3983</v>
+        <v>1.304</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3924</v>
+        <v>0.4394</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.3264</v>
+        <v>-1.3213</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.7927999999999999</v>
+        <v>-0.7803</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5337</v>
+        <v>-0.541</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1317,58 +1317,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2336</v>
+        <v>0.2204</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2455</v>
+        <v>-2.1315</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4791</v>
+        <v>2.352</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0878</v>
+        <v>0.0679</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2027</v>
+        <v>-1.2188</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2905</v>
+        <v>1.2867</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2372</v>
+        <v>-0.1026</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.716</v>
+        <v>-0.628</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4788</v>
+        <v>0.5254</v>
       </c>
       <c r="M11" t="n">
-        <v>0.325</v>
+        <v>0.1705</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4867</v>
+        <v>-0.5908</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8117</v>
+        <v>0.7613</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6995</v>
+        <v>-0.6885</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3317</v>
+        <v>-2.295</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6322</v>
+        <v>1.6065</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.841</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3234</v>
+        <v>0.266</v>
       </c>
       <c r="U11" t="n">
-        <v>0.522</v>
+        <v>0.575</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1400,67 +1400,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2359</v>
+        <v>-0.1571</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1099</v>
+        <v>0.0326</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.126</v>
+        <v>-0.1897</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0206</v>
+        <v>0.0552</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7373</v>
+        <v>-0.6186</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7167</v>
+        <v>0.6737</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8414</v>
+        <v>-0.6533</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9147999999999999</v>
+        <v>-0.7274</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0741</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8209</v>
+        <v>0.7084</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1775</v>
+        <v>0.1088</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6433</v>
+        <v>0.5996</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6995</v>
+        <v>0.6885</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6995</v>
+        <v>0.6885</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1525</v>
+        <v>0.1812</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7316</v>
+        <v>0.6859</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-0.5046</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0673</v>
+        <v>-1.082</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0673</v>
+        <v>-1.082</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1483,67 +1483,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.906</v>
+        <v>-3.842</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.334</v>
+        <v>-3.1289</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.572</v>
+        <v>-0.7131</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.9073</v>
+        <v>-2.8057</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4186</v>
+        <v>-0.4174</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.4887</v>
+        <v>-2.3883</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.3619</v>
+        <v>-2.1118</v>
       </c>
       <c r="K13" t="n">
-        <v>0.235</v>
+        <v>0.3439</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.5969</v>
+        <v>-2.4557</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5454</v>
+        <v>-0.6939</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6536</v>
+        <v>-0.7614</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1081</v>
+        <v>0.0674</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2332</v>
+        <v>-0.2295</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1658</v>
+        <v>-1.1475</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9327</v>
+        <v>0.918</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8355</v>
+        <v>0.8163</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1937</v>
+        <v>0.1304</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6417</v>
+        <v>0.6859</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.601</v>
+        <v>-1.623</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.601</v>
+        <v>-1.623</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1566,67 +1566,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>32.2098</v>
+        <v>32.2019</v>
       </c>
       <c r="E14" t="n">
-        <v>17.2742</v>
+        <v>18.5573</v>
       </c>
       <c r="F14" t="n">
-        <v>14.9351</v>
+        <v>13.6446</v>
       </c>
       <c r="G14" t="n">
-        <v>30.9228</v>
+        <v>30.9165</v>
       </c>
       <c r="H14" t="n">
-        <v>11.7394</v>
+        <v>11.5828</v>
       </c>
       <c r="I14" t="n">
-        <v>19.1835</v>
+        <v>19.3337</v>
       </c>
       <c r="J14" t="n">
-        <v>21.9464</v>
+        <v>23.7</v>
       </c>
       <c r="K14" t="n">
-        <v>9.887600000000001</v>
+        <v>10.9354</v>
       </c>
       <c r="L14" t="n">
-        <v>12.0588</v>
+        <v>12.7648</v>
       </c>
       <c r="M14" t="n">
-        <v>8.976499999999998</v>
+        <v>7.2165</v>
       </c>
       <c r="N14" t="n">
-        <v>1.8519</v>
+        <v>0.6474000000000003</v>
       </c>
       <c r="O14" t="n">
-        <v>7.1245</v>
+        <v>6.5689</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0001000000000001278</v>
+        <v>-2.775557561562891e-17</v>
       </c>
       <c r="Q14" t="n">
-        <v>-12.8241</v>
+        <v>-12.6224</v>
       </c>
       <c r="R14" t="n">
-        <v>12.8242</v>
+        <v>12.6225</v>
       </c>
       <c r="S14" t="n">
-        <v>6.09</v>
+        <v>6.1547</v>
       </c>
       <c r="T14" t="n">
-        <v>6.2767</v>
+        <v>5.554900000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1869</v>
+        <v>0.5998999999999998</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.803</v>
+        <v>-4.8691</v>
       </c>
       <c r="W14" t="n">
-        <v>1.8755</v>
+        <v>1.9247</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.678499999999999</v>
+        <v>-6.793800000000001</v>
       </c>
       <c r="Y14" t="inlineStr"/>
     </row>
@@ -1645,40 +1645,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3709</v>
+        <v>1.328</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9986</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3723</v>
+        <v>0.3305</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5981</v>
+        <v>0.5426</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9283</v>
+        <v>0.8761</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3301</v>
+        <v>-0.3335</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6206</v>
+        <v>0.6338</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5839</v>
+        <v>0.5968</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0367</v>
+        <v>0.0371</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0225</v>
+        <v>-0.0912</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3444</v>
+        <v>0.2793</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3668</v>
+        <v>-0.3705</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1690,22 +1690,22 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5537</v>
+        <v>-0.5359</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1557</v>
+        <v>-0.1773</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.398</v>
+        <v>-0.3586</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3264</v>
+        <v>1.3213</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5337</v>
+        <v>0.541</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.7803</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1728,58 +1728,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2245</v>
+        <v>-0.287</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4709</v>
+        <v>-0.4644</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2464</v>
+        <v>0.1774</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4639</v>
+        <v>-0.4904</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2397</v>
+        <v>0.2034</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7036</v>
+        <v>-0.6939</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2259</v>
+        <v>0.2828</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0677</v>
+        <v>1.0912</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.8418</v>
+        <v>-0.8084</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6898</v>
+        <v>-0.7732</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.828</v>
+        <v>-0.8878</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1383</v>
+        <v>0.1146</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1658</v>
+        <v>-1.1475</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1658</v>
+        <v>1.1475</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2393</v>
+        <v>0.2034</v>
       </c>
       <c r="T16" t="n">
-        <v>0.469</v>
+        <v>0.4003</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2297</v>
+        <v>-0.1969</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1811,64 +1811,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5013</v>
+        <v>-0.4591</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2497</v>
+        <v>0.436</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.751</v>
+        <v>-0.8951</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1547</v>
+        <v>-0.1703</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0859</v>
+        <v>1.0995</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.2407</v>
+        <v>-1.2698</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3514</v>
+        <v>1.5294</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5696</v>
+        <v>1.7079</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.2182</v>
+        <v>-0.1786</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5061</v>
+        <v>-1.6997</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4837</v>
+        <v>-0.6085</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0225</v>
+        <v>-1.0912</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9327</v>
+        <v>-0.918</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3317</v>
+        <v>-2.295</v>
       </c>
       <c r="R17" t="n">
-        <v>1.399</v>
+        <v>1.377</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6185</v>
+        <v>-0.6037</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0254</v>
+        <v>-0.0313</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6439</v>
+        <v>-0.5724</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2046</v>
+        <v>1.2329</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2046</v>
+        <v>1.2329</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1894,58 +1894,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2692</v>
+        <v>-1.401</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0667</v>
+        <v>0.0135</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3359</v>
+        <v>-1.4145</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.0104</v>
+        <v>-2.0934</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7517</v>
+        <v>-1.7903</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2587</v>
+        <v>-0.3031</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0834</v>
+        <v>0.0853</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0834</v>
+        <v>0.0853</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.0938</v>
+        <v>-2.1786</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.8351</v>
+        <v>-1.8756</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2587</v>
+        <v>-0.3031</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1658</v>
+        <v>1.1475</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1658</v>
+        <v>1.1475</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4246</v>
+        <v>-0.4551</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0167</v>
+        <v>-0.0717</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4079</v>
+        <v>-0.3834</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1977,58 +1977,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8027</v>
+        <v>-1.9419</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3317</v>
+        <v>-0.3085</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.471</v>
+        <v>-1.6334</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6947</v>
+        <v>-0.797</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3626</v>
+        <v>0.2875</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0572</v>
+        <v>-1.0845</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3507</v>
+        <v>2.4403</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0187</v>
+        <v>2.0631</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3321</v>
+        <v>0.3772</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.0454</v>
+        <v>-3.2373</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6561</v>
+        <v>-1.7756</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3893</v>
+        <v>-1.4617</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4663</v>
+        <v>-0.459</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.5649</v>
+        <v>-2.5244</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0985</v>
+        <v>2.0655</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6417</v>
+        <v>-0.6859</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1176</v>
+        <v>-0.2243</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5241</v>
+        <v>-0.4616</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2060,64 +2060,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0158</v>
+        <v>-2.9645</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5549</v>
+        <v>-2.3833</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4609</v>
+        <v>-0.5812</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.1628</v>
+        <v>-4.1675</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.1592</v>
+        <v>-3.1873</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0036</v>
+        <v>-0.9802</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.8883</v>
+        <v>-2.7061</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.3419</v>
+        <v>-2.2378</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5464</v>
+        <v>-0.4683</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2745</v>
+        <v>-1.4614</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8173</v>
+        <v>-0.9495</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4572</v>
+        <v>-0.5119</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.399</v>
+        <v>-1.377</v>
       </c>
       <c r="R20" t="n">
-        <v>1.399</v>
+        <v>1.377</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9876</v>
+        <v>-0.961</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4022</v>
+        <v>-0.4642</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5854</v>
+        <v>-0.4968</v>
       </c>
       <c r="V20" t="n">
-        <v>2.1347</v>
+        <v>2.164</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1347</v>
+        <v>2.164</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2143,58 +2143,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.41</v>
+        <v>-3.2424</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6365</v>
+        <v>-0.3381</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7735</v>
+        <v>-2.9043</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.5174</v>
+        <v>-4.3142</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9224</v>
+        <v>-0.6833</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.595</v>
+        <v>-3.6309</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2057</v>
+        <v>-0.8179999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4046</v>
+        <v>0.7248</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.6102</v>
+        <v>-1.5428</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.3117</v>
+        <v>-3.4963</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.327</v>
+        <v>-1.4081</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.9847</v>
+        <v>-2.0881</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9327</v>
+        <v>0.918</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2332</v>
+        <v>-0.2295</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1658</v>
+        <v>1.1475</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1747</v>
+        <v>0.1539</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8024</v>
+        <v>0.7093</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6277</v>
+        <v>-0.5555</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2226,58 +2226,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6581</v>
+        <v>-3.6482</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1392</v>
+        <v>-3.0462</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5189</v>
+        <v>-0.602</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.5497</v>
+        <v>-1.558</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.9899</v>
+        <v>-2.0026</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4402</v>
+        <v>0.4446</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0012</v>
+        <v>-0.8817</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.3333</v>
+        <v>-1.2588</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3321</v>
+        <v>0.3772</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5485</v>
+        <v>-0.6763</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6566</v>
+        <v>-0.7437</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1081</v>
+        <v>0.0674</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.6322</v>
+        <v>-1.6065</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3317</v>
+        <v>-2.295</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6995</v>
+        <v>0.6885</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4762</v>
+        <v>-0.4838</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1937</v>
+        <v>0.1304</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6699000000000001</v>
+        <v>-0.6142</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2309,64 +2309,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8505</v>
+        <v>-3.8445</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7111</v>
+        <v>-1.5927</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1394</v>
+        <v>-2.2517</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.3291</v>
+        <v>-5.3242</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7174</v>
+        <v>-0.7332</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.6117</v>
+        <v>-4.591</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.3796</v>
+        <v>-2.2249</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1091</v>
+        <v>0.1634</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.4887</v>
+        <v>-2.3883</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.9495</v>
+        <v>-3.0993</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8265</v>
+        <v>-0.8966</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.123</v>
+        <v>-2.2027</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6995</v>
+        <v>0.6885</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2332</v>
+        <v>-0.2295</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9327</v>
+        <v>0.918</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2883</v>
+        <v>-0.2908</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1657</v>
+        <v>-0.2204</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1226</v>
+        <v>-0.0704</v>
       </c>
       <c r="V23" t="n">
-        <v>1.0673</v>
+        <v>1.082</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0673</v>
+        <v>1.082</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2392,67 +2392,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.5635</v>
+        <v>-4.6566</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8386</v>
+        <v>-0.8031</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.7249</v>
+        <v>-3.8534</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.5714</v>
+        <v>-2.6307</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8250999999999999</v>
+        <v>0.7914</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.3965</v>
+        <v>-3.4221</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4591</v>
+        <v>-0.3663</v>
       </c>
       <c r="K24" t="n">
-        <v>1.1511</v>
+        <v>1.1765</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.6102</v>
+        <v>-1.5428</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.1122</v>
+        <v>-2.2644</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.326</v>
+        <v>-0.3851</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.7862</v>
+        <v>-1.8793</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9327</v>
+        <v>0.918</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9327</v>
+        <v>0.918</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7902</v>
+        <v>-0.7798</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3795</v>
+        <v>-0.4368</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4107</v>
+        <v>-0.3429</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.1347</v>
+        <v>-2.164</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1347</v>
+        <v>-2.164</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>W. VAN BECK</t>
+          <t>M. HUERTAS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.5831</v>
+        <v>-5.5202</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.1529</v>
+        <v>-4.1565</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.4302</v>
+        <v>-1.3636</v>
       </c>
       <c r="G25" t="n">
-        <v>-6.0182</v>
+        <v>-3.9187</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.7523</v>
+        <v>-2.7129</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.2659</v>
+        <v>-1.2058</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.9427</v>
+        <v>-2.4807</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.433</v>
+        <v>-2.4807</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5098</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.0755</v>
+        <v>-1.438</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.3194</v>
+        <v>-0.2322</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.7561</v>
+        <v>-1.2058</v>
       </c>
       <c r="P25" t="n">
-        <v>0.6995</v>
+        <v>-1.377</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.2332</v>
+        <v>-2.295</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9327</v>
+        <v>0.918</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4017</v>
+        <v>-1.3066</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3521</v>
+        <v>-0.4629</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7538</v>
+        <v>-0.8437</v>
       </c>
       <c r="V25" t="n">
-        <v>0.1373</v>
+        <v>1.082</v>
       </c>
       <c r="W25" t="n">
-        <v>0.6709000000000001</v>
+        <v>1.082</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.5337</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>M. HUERTAS</t>
+          <t>W. VAN BECK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2558,67 +2558,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.7017</v>
+        <v>-5.5647</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.4145</v>
+        <v>-1.9988</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.2873</v>
+        <v>-3.5659</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.0487</v>
+        <v>-5.9946</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.888</v>
+        <v>-3.7312</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.1607</v>
+        <v>-2.2635</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.7319</v>
+        <v>-2.7103</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.7319</v>
+        <v>-2.279</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>-0.4313</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.3168</v>
+        <v>-3.2844</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.1561</v>
+        <v>-1.4522</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.1607</v>
+        <v>-1.8322</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.399</v>
+        <v>0.6885</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.3317</v>
+        <v>-0.2295</v>
       </c>
       <c r="R26" t="n">
-        <v>0.9327</v>
+        <v>0.918</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.3213</v>
+        <v>-0.4094</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4182</v>
+        <v>0.2491</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.9031</v>
+        <v>-0.6585</v>
       </c>
       <c r="V26" t="n">
-        <v>1.0673</v>
+        <v>0.1509</v>
       </c>
       <c r="W26" t="n">
-        <v>1.0673</v>
+        <v>0.6919</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>-0.541</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2641,67 +2641,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-32.20950000000001</v>
+        <v>-32.2021</v>
       </c>
       <c r="E27" t="n">
-        <v>-14.9353</v>
+        <v>-13.6446</v>
       </c>
       <c r="F27" t="n">
-        <v>-17.2743</v>
+        <v>-18.5572</v>
       </c>
       <c r="G27" t="n">
-        <v>-30.9229</v>
+        <v>-30.9164</v>
       </c>
       <c r="H27" t="n">
-        <v>-11.7393</v>
+        <v>-11.5829</v>
       </c>
       <c r="I27" t="n">
-        <v>-19.1835</v>
+        <v>-19.3337</v>
       </c>
       <c r="J27" t="n">
-        <v>-8.9765</v>
+        <v>-7.2164</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.851999999999999</v>
+        <v>-0.6473</v>
       </c>
       <c r="L27" t="n">
-        <v>-7.124400000000001</v>
+        <v>-6.569</v>
       </c>
       <c r="M27" t="n">
-        <v>-21.9463</v>
+        <v>-23.7001</v>
       </c>
       <c r="N27" t="n">
-        <v>-9.8874</v>
+        <v>-10.9356</v>
       </c>
       <c r="O27" t="n">
-        <v>-12.0588</v>
+        <v>-12.7645</v>
       </c>
       <c r="P27" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>-12.8244</v>
+        <v>-12.6224</v>
       </c>
       <c r="R27" t="n">
-        <v>12.8242</v>
+        <v>12.6225</v>
       </c>
       <c r="S27" t="n">
-        <v>-6.089799999999999</v>
+        <v>-6.1547</v>
       </c>
       <c r="T27" t="n">
-        <v>0.1869999999999999</v>
+        <v>-0.5998</v>
       </c>
       <c r="U27" t="n">
-        <v>-6.276800000000001</v>
+        <v>-5.5549</v>
       </c>
       <c r="V27" t="n">
-        <v>4.802899999999999</v>
+        <v>4.8691</v>
       </c>
       <c r="W27" t="n">
-        <v>6.6785</v>
+        <v>6.793800000000001</v>
       </c>
       <c r="X27" t="n">
-        <v>-1.8756</v>
+        <v>-1.9247</v>
       </c>
       <c r="Y27" t="inlineStr"/>
     </row>

--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105360_W4.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105360_W4.xlsx
@@ -570,67 +570,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.2713</v>
+        <v>8.201700000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9302</v>
+        <v>6.7411</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3411</v>
+        <v>1.4607</v>
       </c>
       <c r="G2" t="n">
-        <v>7.1277</v>
+        <v>7.0096</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4766</v>
+        <v>3.4098</v>
       </c>
       <c r="I2" t="n">
-        <v>3.6511</v>
+        <v>3.5998</v>
       </c>
       <c r="J2" t="n">
-        <v>5.7725</v>
+        <v>5.6256</v>
       </c>
       <c r="K2" t="n">
-        <v>2.721</v>
+        <v>2.6291</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0515</v>
+        <v>2.9966</v>
       </c>
       <c r="M2" t="n">
-        <v>1.3552</v>
+        <v>1.384</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7556</v>
+        <v>0.7808</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5996</v>
+        <v>0.6032</v>
       </c>
       <c r="P2" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3077</v>
+        <v>0.3203</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6168</v>
+        <v>0.5834</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.309</v>
+        <v>-0.263</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.541</v>
+        <v>-0.5321</v>
       </c>
       <c r="W2" t="n">
-        <v>0.541</v>
+        <v>0.5321</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -653,64 +653,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.2562</v>
+        <v>7.188</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3215</v>
+        <v>5.0994</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9347</v>
+        <v>2.0885</v>
       </c>
       <c r="G3" t="n">
-        <v>5.9134</v>
+        <v>5.848</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0096</v>
+        <v>1.9896</v>
       </c>
       <c r="I3" t="n">
-        <v>3.9038</v>
+        <v>3.8584</v>
       </c>
       <c r="J3" t="n">
-        <v>6.0663</v>
+        <v>5.9449</v>
       </c>
       <c r="K3" t="n">
-        <v>2.7622</v>
+        <v>2.6897</v>
       </c>
       <c r="L3" t="n">
-        <v>3.3042</v>
+        <v>3.2552</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1529</v>
+        <v>-0.0968</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7524999999999999</v>
+        <v>-0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5996</v>
+        <v>0.6032</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4083</v>
+        <v>1.4457</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4681</v>
+        <v>0.4302</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9401</v>
+        <v>1.0155</v>
       </c>
       <c r="V3" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="W3" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -736,67 +736,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4924</v>
+        <v>4.5225</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4875</v>
+        <v>3.3447</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0048</v>
+        <v>1.1778</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1163</v>
+        <v>3.0844</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0313</v>
+        <v>1.0083</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0851</v>
+        <v>2.0761</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5201</v>
+        <v>1.4382</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1493</v>
+        <v>0.0839</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3709</v>
+        <v>1.3543</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5962</v>
+        <v>1.6461</v>
       </c>
       <c r="N4" t="n">
-        <v>0.882</v>
+        <v>0.9243</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.7218</v>
       </c>
       <c r="P4" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="S4" t="n">
-        <v>0.15</v>
+        <v>0.1686</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8854</v>
+        <v>0.8423</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7354000000000001</v>
+        <v>-0.6738</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="W4" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2329</v>
+        <v>-1.1984</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -819,67 +819,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.3695</v>
+        <v>4.3446</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2846</v>
+        <v>4.1254</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0849</v>
+        <v>0.2192</v>
       </c>
       <c r="G5" t="n">
-        <v>5.7188</v>
+        <v>5.6523</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8249</v>
+        <v>0.8319</v>
       </c>
       <c r="I5" t="n">
-        <v>4.8939</v>
+        <v>4.8204</v>
       </c>
       <c r="J5" t="n">
-        <v>4.9223</v>
+        <v>4.8093</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4192</v>
+        <v>0.3877</v>
       </c>
       <c r="L5" t="n">
-        <v>4.5031</v>
+        <v>4.4216</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7966</v>
+        <v>0.8429</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4057</v>
+        <v>0.4442</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3908</v>
+        <v>0.3987</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.459</v>
+        <v>-0.4679</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1917</v>
+        <v>0.2243</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5098</v>
+        <v>0.4859</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3182</v>
+        <v>-0.2616</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -902,58 +902,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.3109</v>
+        <v>3.2243</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6878</v>
+        <v>0.4995</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6231</v>
+        <v>2.7248</v>
       </c>
       <c r="G6" t="n">
-        <v>5.7558</v>
+        <v>5.6963</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2026</v>
+        <v>3.1594</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5532</v>
+        <v>2.5368</v>
       </c>
       <c r="J6" t="n">
-        <v>4.0389</v>
+        <v>3.9508</v>
       </c>
       <c r="K6" t="n">
-        <v>2.7792</v>
+        <v>2.7063</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2597</v>
+        <v>1.2445</v>
       </c>
       <c r="M6" t="n">
-        <v>1.7169</v>
+        <v>1.7455</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4234</v>
+        <v>0.4532</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2935</v>
+        <v>1.2923</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.0655</v>
+        <v>-2.1057</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.4424</v>
+        <v>-3.5096</v>
       </c>
       <c r="R6" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3794</v>
+        <v>-0.3662</v>
       </c>
       <c r="T6" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.0584</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4707</v>
+        <v>-0.4245</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -985,58 +985,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.47</v>
+        <v>2.4979</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8191000000000001</v>
+        <v>0.7149</v>
       </c>
       <c r="F7" t="n">
-        <v>1.651</v>
+        <v>1.7829</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4086</v>
+        <v>1.3976</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2137</v>
+        <v>2.1965</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.805</v>
+        <v>-0.7989000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1358</v>
+        <v>0.0745</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4934</v>
+        <v>1.4337</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3575</v>
+        <v>-1.3592</v>
       </c>
       <c r="M7" t="n">
-        <v>1.2728</v>
+        <v>1.3231</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.7628</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5525</v>
+        <v>0.5603</v>
       </c>
       <c r="P7" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1434</v>
+        <v>0.1644</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6833</v>
+        <v>0.6404</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.476</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1068,58 +1068,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.3383</v>
+        <v>2.3615</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0392</v>
+        <v>-0.0494</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2991</v>
+        <v>2.4108</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9862</v>
+        <v>1.991</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9184</v>
+        <v>0.927</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0678</v>
+        <v>1.0639</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4188</v>
+        <v>1.3852</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1594</v>
+        <v>1.129</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2594</v>
+        <v>0.2562</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5674</v>
+        <v>0.6058</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.241</v>
+        <v>-0.2019</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8084</v>
+        <v>0.8077</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R8" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1226</v>
+        <v>0.1365</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2321</v>
+        <v>-0.2647</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3547</v>
+        <v>0.4013</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1151,67 +1151,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.2212</v>
+        <v>2.2477</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4893</v>
+        <v>1.3984</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7319</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2026</v>
+        <v>2.2009</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1552</v>
+        <v>-0.1266</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3577</v>
+        <v>2.3275</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4907</v>
+        <v>2.4458</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4092</v>
+        <v>0.3985</v>
       </c>
       <c r="L9" t="n">
-        <v>2.0815</v>
+        <v>2.0473</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2881</v>
+        <v>-0.2449</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5644</v>
+        <v>-0.525</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2763</v>
+        <v>0.2801</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.459</v>
+        <v>-0.4679</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.649</v>
       </c>
       <c r="T9" t="n">
-        <v>0.146</v>
+        <v>0.1225</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4825</v>
+        <v>0.5266</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1234,67 +1234,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2508</v>
+        <v>1.2659</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7259</v>
+        <v>0.6325</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5248</v>
+        <v>0.6334</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3697</v>
+        <v>0.3639</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3157</v>
+        <v>0.3033</v>
       </c>
       <c r="I10" t="n">
-        <v>0.054</v>
+        <v>0.0605</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2023</v>
+        <v>0.1581</v>
       </c>
       <c r="K10" t="n">
-        <v>0.054</v>
+        <v>0.0117</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1482</v>
+        <v>0.1464</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1674</v>
+        <v>0.2058</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2617</v>
+        <v>0.2917</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.0859</v>
       </c>
       <c r="P10" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="S10" t="n">
-        <v>1.7434</v>
+        <v>1.7617</v>
       </c>
       <c r="T10" t="n">
-        <v>1.304</v>
+        <v>1.2699</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4394</v>
+        <v>0.4918</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.3213</v>
+        <v>-1.3276</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.7803</v>
+        <v>-0.7955</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.541</v>
+        <v>-0.5321</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1317,58 +1317,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2204</v>
+        <v>0.2468</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1315</v>
+        <v>-2.2539</v>
       </c>
       <c r="F11" t="n">
-        <v>2.352</v>
+        <v>2.5007</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0679</v>
+        <v>0.0838</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2188</v>
+        <v>-1.1909</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2867</v>
+        <v>1.2748</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1026</v>
+        <v>-0.1424</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.628</v>
+        <v>-0.6524</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5254</v>
+        <v>0.51</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1705</v>
+        <v>0.2263</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5908</v>
+        <v>-0.5385</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7613</v>
+        <v>0.7647</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6885</v>
+        <v>-0.7019</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6065</v>
+        <v>1.6378</v>
       </c>
       <c r="S11" t="n">
-        <v>0.841</v>
+        <v>0.8649</v>
       </c>
       <c r="T11" t="n">
-        <v>0.266</v>
+        <v>0.2282</v>
       </c>
       <c r="U11" t="n">
-        <v>0.575</v>
+        <v>0.6367</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1400,67 +1400,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1571</v>
+        <v>-0.1309</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0326</v>
+        <v>-0.0458</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1897</v>
+        <v>-0.0852</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0552</v>
+        <v>0.0208</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6186</v>
+        <v>-0.6556</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6737</v>
+        <v>0.6764</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6533</v>
+        <v>-0.717</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7274</v>
+        <v>-0.7902</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0741</v>
+        <v>0.0732</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7084</v>
+        <v>0.7378</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1088</v>
+        <v>0.1346</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5996</v>
+        <v>0.6032</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1812</v>
+        <v>0.2104</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6859</v>
+        <v>0.6712</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5046</v>
+        <v>-0.4608</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1483,67 +1483,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.842</v>
+        <v>-3.8</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.1289</v>
+        <v>-3.2547</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7131</v>
+        <v>-0.5453</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.8057</v>
+        <v>-2.7971</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4174</v>
+        <v>-0.4106</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.3883</v>
+        <v>-2.3865</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.1118</v>
+        <v>-2.1682</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3439</v>
+        <v>0.2939</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.4557</v>
+        <v>-2.4621</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6939</v>
+        <v>-0.6289</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7614</v>
+        <v>-0.7045</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0674</v>
+        <v>0.0756</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R13" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8163</v>
+        <v>0.8272</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1304</v>
+        <v>0.0834</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6859</v>
+        <v>0.7439</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.623</v>
+        <v>-1.5962</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.623</v>
+        <v>-1.5962</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1566,67 +1566,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>32.2019</v>
+        <v>32.17000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>18.5573</v>
+        <v>16.9521</v>
       </c>
       <c r="F14" t="n">
-        <v>13.6446</v>
+        <v>15.2176</v>
       </c>
       <c r="G14" t="n">
-        <v>30.9165</v>
+        <v>30.5515</v>
       </c>
       <c r="H14" t="n">
-        <v>11.5828</v>
+        <v>11.4421</v>
       </c>
       <c r="I14" t="n">
-        <v>19.3337</v>
+        <v>19.1092</v>
       </c>
       <c r="J14" t="n">
-        <v>23.7</v>
+        <v>22.8048</v>
       </c>
       <c r="K14" t="n">
-        <v>10.9354</v>
+        <v>10.3209</v>
       </c>
       <c r="L14" t="n">
-        <v>12.7648</v>
+        <v>12.484</v>
       </c>
       <c r="M14" t="n">
-        <v>7.2165</v>
+        <v>7.746700000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6474000000000003</v>
+        <v>1.1217</v>
       </c>
       <c r="O14" t="n">
-        <v>6.5689</v>
+        <v>6.624900000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.775557561562891e-17</v>
+        <v>-2.498001805406602e-16</v>
       </c>
       <c r="Q14" t="n">
-        <v>-12.6224</v>
+        <v>-12.8686</v>
       </c>
       <c r="R14" t="n">
-        <v>12.6225</v>
+        <v>12.8683</v>
       </c>
       <c r="S14" t="n">
-        <v>6.1547</v>
+        <v>6.406800000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>5.554900000000001</v>
+        <v>5.1511</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5998999999999998</v>
+        <v>1.2561</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.8691</v>
+        <v>-4.788600000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>1.9247</v>
+        <v>1.8648</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.793800000000001</v>
+        <v>-6.6533</v>
       </c>
       <c r="Y14" t="inlineStr"/>
     </row>
@@ -1645,40 +1645,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.328</v>
+        <v>1.3409</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3305</v>
+        <v>0.3918</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5426</v>
+        <v>0.5523</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8761</v>
+        <v>0.8817</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3335</v>
+        <v>-0.3294</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6338</v>
+        <v>0.6177</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5968</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0371</v>
+        <v>0.0366</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0912</v>
+        <v>-0.0654</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2793</v>
+        <v>0.3006</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3705</v>
+        <v>-0.366</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1690,22 +1690,22 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5359</v>
+        <v>-0.5389</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1773</v>
+        <v>-0.2006</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3586</v>
+        <v>-0.3383</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3213</v>
+        <v>1.3276</v>
       </c>
       <c r="W15" t="n">
-        <v>0.541</v>
+        <v>0.5321</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7803</v>
+        <v>0.7955</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1728,58 +1728,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.287</v>
+        <v>-0.2937</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4644</v>
+        <v>-0.5573</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1774</v>
+        <v>0.2636</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4904</v>
+        <v>-0.4746</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2034</v>
+        <v>0.2145</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6939</v>
+        <v>-0.6891</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2828</v>
+        <v>0.2549</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0912</v>
+        <v>1.0626</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.8084</v>
+        <v>-0.8077</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7732</v>
+        <v>-0.7295</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8878</v>
+        <v>-0.8481</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1146</v>
+        <v>0.1186</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2034</v>
+        <v>0.1809</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4003</v>
+        <v>0.3577</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1969</v>
+        <v>-0.1768</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1811,64 +1811,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4591</v>
+        <v>-0.525</v>
       </c>
       <c r="E17" t="n">
-        <v>0.436</v>
+        <v>0.2172</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8951</v>
+        <v>-0.7422</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1703</v>
+        <v>-0.1761</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0995</v>
+        <v>1.0747</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.2698</v>
+        <v>-1.2508</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5294</v>
+        <v>1.4367</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7079</v>
+        <v>1.6222</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1786</v>
+        <v>-0.1854</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6997</v>
+        <v>-1.6129</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6085</v>
+        <v>-0.5475</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0912</v>
+        <v>-1.0654</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.918</v>
+        <v>-0.9359</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R17" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6037</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0313</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5724</v>
+        <v>-0.5332</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2329</v>
+        <v>1.1984</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2329</v>
+        <v>1.1984</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1894,58 +1894,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.401</v>
+        <v>-1.3584</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0135</v>
+        <v>-0.0355</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4145</v>
+        <v>-1.3228</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.0934</v>
+        <v>-2.0337</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7903</v>
+        <v>-1.7433</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3031</v>
+        <v>-0.2904</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0853</v>
+        <v>0.083</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0853</v>
+        <v>0.083</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1786</v>
+        <v>-2.1167</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.8756</v>
+        <v>-1.8263</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3031</v>
+        <v>-0.2904</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4551</v>
+        <v>-0.4945</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0717</v>
+        <v>-0.1186</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3834</v>
+        <v>-0.376</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1977,58 +1977,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9419</v>
+        <v>-1.9669</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3085</v>
+        <v>-0.519</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6334</v>
+        <v>-1.4479</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.797</v>
+        <v>-0.7551</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2875</v>
+        <v>0.3127</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0845</v>
+        <v>-1.0678</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4403</v>
+        <v>2.3725</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0631</v>
+        <v>2.0089</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3772</v>
+        <v>0.3636</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.2373</v>
+        <v>-3.1276</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7756</v>
+        <v>-1.6962</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4617</v>
+        <v>-1.4314</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.459</v>
+        <v>-0.4679</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.5244</v>
+        <v>-2.5737</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0655</v>
+        <v>2.1057</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6859</v>
+        <v>-0.7439</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2243</v>
+        <v>-0.3179</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4616</v>
+        <v>-0.426</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2060,64 +2060,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9645</v>
+        <v>-2.938</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3833</v>
+        <v>-2.5262</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5812</v>
+        <v>-0.4118</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.1675</v>
+        <v>-4.0956</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.1873</v>
+        <v>-3.12</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9802</v>
+        <v>-0.9756</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.7061</v>
+        <v>-2.7212</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.2378</v>
+        <v>-2.2405</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4683</v>
+        <v>-0.4807</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4614</v>
+        <v>-1.3744</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9495</v>
+        <v>-0.8794999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5119</v>
+        <v>-0.4949</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.377</v>
+        <v>-1.4038</v>
       </c>
       <c r="R20" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.961</v>
+        <v>-0.9707</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4642</v>
+        <v>-0.5294</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4968</v>
+        <v>-0.4412</v>
       </c>
       <c r="V20" t="n">
-        <v>2.164</v>
+        <v>2.1282</v>
       </c>
       <c r="W20" t="n">
-        <v>2.164</v>
+        <v>2.1282</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2143,58 +2143,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2424</v>
+        <v>-3.2769</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3381</v>
+        <v>-0.5361</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.9043</v>
+        <v>-2.7408</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.3142</v>
+        <v>-4.3548</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6833</v>
+        <v>-0.7677</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.6309</v>
+        <v>-3.5871</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8179999999999999</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7248</v>
+        <v>0.5829</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.5428</v>
+        <v>-1.5422</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.4963</v>
+        <v>-3.3956</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4081</v>
+        <v>-1.3507</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.0881</v>
+        <v>-2.0449</v>
       </c>
       <c r="P21" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1539</v>
+        <v>0.142</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7093</v>
+        <v>0.6571</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5555</v>
+        <v>-0.5151</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2226,58 +2226,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6482</v>
+        <v>-3.6664</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0462</v>
+        <v>-3.1595</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.602</v>
+        <v>-0.5069</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.558</v>
+        <v>-1.523</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.0026</v>
+        <v>-1.9623</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4446</v>
+        <v>0.4392</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8817</v>
+        <v>-0.9031</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2588</v>
+        <v>-1.2667</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3772</v>
+        <v>0.3636</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6763</v>
+        <v>-0.6199</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7437</v>
+        <v>-0.6955</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0674</v>
+        <v>0.0756</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.6065</v>
+        <v>-1.6378</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4838</v>
+        <v>-0.5056</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1304</v>
+        <v>0.0834</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6142</v>
+        <v>-0.589</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2309,64 +2309,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8445</v>
+        <v>-3.8001</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5927</v>
+        <v>-1.6894</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2517</v>
+        <v>-2.1107</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.3242</v>
+        <v>-5.2639</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7332</v>
+        <v>-0.7139</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.591</v>
+        <v>-4.55</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.2249</v>
+        <v>-2.2478</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1634</v>
+        <v>0.1387</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.3883</v>
+        <v>-2.3865</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.0993</v>
+        <v>-3.0161</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8966</v>
+        <v>-0.8526</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.2027</v>
+        <v>-2.1635</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="R23" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2908</v>
+        <v>-0.3022</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2204</v>
+        <v>-0.2718</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0704</v>
+        <v>-0.0305</v>
       </c>
       <c r="V23" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="W23" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2392,67 +2392,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6566</v>
+        <v>-4.5805</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8031</v>
+        <v>-0.894</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.8534</v>
+        <v>-3.6865</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.6307</v>
+        <v>-2.5915</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7914</v>
+        <v>0.7911</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.4221</v>
+        <v>-3.3826</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3663</v>
+        <v>-0.3966</v>
       </c>
       <c r="K24" t="n">
-        <v>1.1765</v>
+        <v>1.1456</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.5428</v>
+        <v>-1.5422</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.2644</v>
+        <v>-2.1949</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3851</v>
+        <v>-0.3545</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.8793</v>
+        <v>-1.8404</v>
       </c>
       <c r="P24" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7798</v>
+        <v>-0.7966</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4368</v>
+        <v>-0.4974</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3429</v>
+        <v>-0.2992</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.164</v>
+        <v>-2.1282</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.164</v>
+        <v>-2.1282</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. HUERTAS</t>
+          <t>W. VAN BECK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.5202</v>
+        <v>-5.5085</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.1565</v>
+        <v>-2.139</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.3636</v>
+        <v>-3.3695</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.9187</v>
+        <v>-5.9157</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.7129</v>
+        <v>-3.6741</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.2058</v>
+        <v>-2.2416</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.4807</v>
+        <v>-2.7451</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.4807</v>
+        <v>-2.301</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>-0.4441</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.438</v>
+        <v>-3.1706</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.2322</v>
+        <v>-1.3731</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.2058</v>
+        <v>-1.7975</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.377</v>
+        <v>0.7019</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.295</v>
+        <v>-0.234</v>
       </c>
       <c r="R25" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3066</v>
+        <v>-0.429</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4629</v>
+        <v>0.1738</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8437</v>
+        <v>-0.6028</v>
       </c>
       <c r="V25" t="n">
-        <v>1.082</v>
+        <v>0.1343</v>
       </c>
       <c r="W25" t="n">
-        <v>1.082</v>
+        <v>0.6664</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-0.5321</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>W. VAN BECK</t>
+          <t>M. HUERTAS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2558,67 +2558,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.5647</v>
+        <v>-5.5965</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.9988</v>
+        <v>-4.3281</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.5659</v>
+        <v>-1.2685</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.9946</v>
+        <v>-3.9198</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.7312</v>
+        <v>-2.7358</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.2635</v>
+        <v>-1.184</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.7103</v>
+        <v>-2.5384</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.279</v>
+        <v>-2.5384</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.4313</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-3.2844</v>
+        <v>-1.3814</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.4522</v>
+        <v>-0.1975</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.8322</v>
+        <v>-1.184</v>
       </c>
       <c r="P26" t="n">
-        <v>0.6885</v>
+        <v>-1.4038</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.2295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R26" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.4094</v>
+        <v>-1.337</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2491</v>
+        <v>-0.5141</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.6585</v>
+        <v>-0.8229</v>
       </c>
       <c r="V26" t="n">
-        <v>0.1509</v>
+        <v>1.0641</v>
       </c>
       <c r="W26" t="n">
-        <v>0.6919</v>
+        <v>1.0641</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.541</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2641,67 +2641,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-32.2021</v>
+        <v>-32.17</v>
       </c>
       <c r="E27" t="n">
-        <v>-13.6446</v>
+        <v>-15.2178</v>
       </c>
       <c r="F27" t="n">
-        <v>-18.5572</v>
+        <v>-16.9522</v>
       </c>
       <c r="G27" t="n">
-        <v>-30.9164</v>
+        <v>-30.5515</v>
       </c>
       <c r="H27" t="n">
-        <v>-11.5829</v>
+        <v>-11.4424</v>
       </c>
       <c r="I27" t="n">
-        <v>-19.3337</v>
+        <v>-19.1092</v>
       </c>
       <c r="J27" t="n">
-        <v>-7.2164</v>
+        <v>-7.7466</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.6473</v>
+        <v>-1.1216</v>
       </c>
       <c r="L27" t="n">
-        <v>-6.569</v>
+        <v>-6.625</v>
       </c>
       <c r="M27" t="n">
-        <v>-23.7001</v>
+        <v>-22.805</v>
       </c>
       <c r="N27" t="n">
-        <v>-10.9356</v>
+        <v>-10.3209</v>
       </c>
       <c r="O27" t="n">
-        <v>-12.7645</v>
+        <v>-12.4842</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>9.999999999998899e-05</v>
       </c>
       <c r="Q27" t="n">
-        <v>-12.6224</v>
+        <v>-12.8685</v>
       </c>
       <c r="R27" t="n">
-        <v>12.6225</v>
+        <v>12.8685</v>
       </c>
       <c r="S27" t="n">
-        <v>-6.1547</v>
+        <v>-6.4069</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.5998</v>
+        <v>-1.256</v>
       </c>
       <c r="U27" t="n">
-        <v>-5.5549</v>
+        <v>-5.151</v>
       </c>
       <c r="V27" t="n">
-        <v>4.8691</v>
+        <v>4.788499999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>6.793800000000001</v>
+        <v>6.6533</v>
       </c>
       <c r="X27" t="n">
-        <v>-1.9247</v>
+        <v>-1.8648</v>
       </c>
       <c r="Y27" t="inlineStr"/>
     </row>

--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105360_W4.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105360_W4.xlsx
@@ -570,67 +570,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.201700000000001</v>
+        <v>8.231299999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7411</v>
+        <v>6.8193</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4607</v>
+        <v>1.412</v>
       </c>
       <c r="G2" t="n">
-        <v>7.0096</v>
+        <v>7.0631</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4098</v>
+        <v>3.4482</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5998</v>
+        <v>3.6149</v>
       </c>
       <c r="J2" t="n">
-        <v>5.6256</v>
+        <v>5.6629</v>
       </c>
       <c r="K2" t="n">
-        <v>2.6291</v>
+        <v>2.6598</v>
       </c>
       <c r="L2" t="n">
-        <v>2.9966</v>
+        <v>3.0032</v>
       </c>
       <c r="M2" t="n">
-        <v>1.384</v>
+        <v>1.4002</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7808</v>
+        <v>0.7884</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6032</v>
+        <v>0.6117</v>
       </c>
       <c r="P2" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3203</v>
+        <v>0.3116</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5834</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.263</v>
+        <v>-0.3089</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.5321</v>
+        <v>-0.5359</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5321</v>
+        <v>0.5359</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -653,64 +653,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.188</v>
+        <v>7.227</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0994</v>
+        <v>5.2092</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0885</v>
+        <v>2.0178</v>
       </c>
       <c r="G3" t="n">
-        <v>5.848</v>
+        <v>5.8908</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9896</v>
+        <v>2.0115</v>
       </c>
       <c r="I3" t="n">
-        <v>3.8584</v>
+        <v>3.8794</v>
       </c>
       <c r="J3" t="n">
-        <v>5.9449</v>
+        <v>5.9881</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6897</v>
+        <v>2.7204</v>
       </c>
       <c r="L3" t="n">
-        <v>3.2552</v>
+        <v>3.2676</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0968</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7</v>
+        <v>-0.709</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6032</v>
+        <v>0.6117</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3397</v>
+        <v>-2.3207</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4457</v>
+        <v>1.4248</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4302</v>
+        <v>0.4701</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0155</v>
+        <v>0.9547</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -736,67 +736,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5225</v>
+        <v>4.5185</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3447</v>
+        <v>3.4108</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1778</v>
+        <v>1.1077</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0844</v>
+        <v>3.1147</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0083</v>
+        <v>1.0197</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0761</v>
+        <v>2.0949</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4382</v>
+        <v>1.4479</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0839</v>
+        <v>0.0866</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3543</v>
+        <v>1.3613</v>
       </c>
       <c r="M4" t="n">
-        <v>1.6461</v>
+        <v>1.6667</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9243</v>
+        <v>0.9331</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7218</v>
+        <v>0.7336</v>
       </c>
       <c r="P4" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1686</v>
+        <v>0.1527</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8423</v>
+        <v>0.8911</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6738</v>
+        <v>-0.7383999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1984</v>
+        <v>-1.213</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -819,67 +819,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.3446</v>
+        <v>4.3389</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1254</v>
+        <v>4.1767</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2192</v>
+        <v>0.1621</v>
       </c>
       <c r="G5" t="n">
-        <v>5.6523</v>
+        <v>5.6789</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8319</v>
+        <v>0.8406</v>
       </c>
       <c r="I5" t="n">
-        <v>4.8204</v>
+        <v>4.8382</v>
       </c>
       <c r="J5" t="n">
-        <v>4.8093</v>
+        <v>4.8239</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3877</v>
+        <v>0.3927</v>
       </c>
       <c r="L5" t="n">
-        <v>4.4216</v>
+        <v>4.4312</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8429</v>
+        <v>0.855</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4442</v>
+        <v>0.4479</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3987</v>
+        <v>0.4071</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4679</v>
+        <v>-0.4641</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2243</v>
+        <v>0.1959</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4859</v>
+        <v>0.5132</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2616</v>
+        <v>-0.3173</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -902,58 +902,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2243</v>
+        <v>3.2807</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4995</v>
+        <v>0.597</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7248</v>
+        <v>2.6837</v>
       </c>
       <c r="G6" t="n">
-        <v>5.6963</v>
+        <v>5.7516</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1594</v>
+        <v>3.1945</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5368</v>
+        <v>2.5571</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9508</v>
+        <v>3.9882</v>
       </c>
       <c r="K6" t="n">
-        <v>2.7063</v>
+        <v>2.7372</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2445</v>
+        <v>1.251</v>
       </c>
       <c r="M6" t="n">
-        <v>1.7455</v>
+        <v>1.7634</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4532</v>
+        <v>0.4572</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2923</v>
+        <v>1.3062</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.1057</v>
+        <v>-2.0886</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.5096</v>
+        <v>-3.4811</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3662</v>
+        <v>-0.3823</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0584</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4245</v>
+        <v>-0.4721</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -985,58 +985,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4979</v>
+        <v>2.4902</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7149</v>
+        <v>0.7625</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7829</v>
+        <v>1.7277</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3976</v>
+        <v>1.4156</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1965</v>
+        <v>2.2205</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7989000000000001</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0745</v>
+        <v>0.0755</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4337</v>
+        <v>1.4507</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3592</v>
+        <v>-1.3752</v>
       </c>
       <c r="M7" t="n">
-        <v>1.3231</v>
+        <v>1.3402</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7628</v>
+        <v>0.7698</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5603</v>
+        <v>0.5703</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1644</v>
+        <v>0.1463</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6404</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.476</v>
+        <v>-0.5407</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1068,58 +1068,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.3615</v>
+        <v>2.3675</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0494</v>
+        <v>0.0024</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4108</v>
+        <v>2.3651</v>
       </c>
       <c r="G8" t="n">
-        <v>1.991</v>
+        <v>2.0107</v>
       </c>
       <c r="H8" t="n">
-        <v>0.927</v>
+        <v>0.9367</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0639</v>
+        <v>1.0739</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3852</v>
+        <v>1.3995</v>
       </c>
       <c r="K8" t="n">
-        <v>1.129</v>
+        <v>1.1419</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2562</v>
+        <v>0.2575</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6058</v>
+        <v>0.6112</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2019</v>
+        <v>-0.2052</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8077</v>
+        <v>0.8164</v>
       </c>
       <c r="P8" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1365</v>
+        <v>0.1248</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2647</v>
+        <v>-0.2367</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4013</v>
+        <v>0.3614</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1151,67 +1151,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.2477</v>
+        <v>2.2406</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3984</v>
+        <v>1.442</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8493000000000001</v>
+        <v>0.7986</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2009</v>
+        <v>2.21</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1266</v>
+        <v>-0.1287</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3275</v>
+        <v>2.3386</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4458</v>
+        <v>2.4565</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3985</v>
+        <v>0.403</v>
       </c>
       <c r="L9" t="n">
-        <v>2.0473</v>
+        <v>2.0535</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2449</v>
+        <v>-0.2465</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.525</v>
+        <v>-0.5317</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2801</v>
+        <v>0.2852</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4679</v>
+        <v>-0.4641</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="S9" t="n">
-        <v>0.649</v>
+        <v>0.6361</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1225</v>
+        <v>0.1458</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5266</v>
+        <v>0.4903</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1234,67 +1234,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2659</v>
+        <v>1.2724</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6325</v>
+        <v>0.6855</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6334</v>
+        <v>0.5869</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3639</v>
+        <v>0.3713</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3033</v>
+        <v>0.3069</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0605</v>
+        <v>0.0644</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1581</v>
+        <v>0.1601</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0117</v>
+        <v>0.013</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1464</v>
+        <v>0.1472</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2058</v>
+        <v>0.2112</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2917</v>
+        <v>0.294</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0859</v>
+        <v>-0.0828</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="S10" t="n">
-        <v>1.7617</v>
+        <v>1.7619</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2699</v>
+        <v>1.3144</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4918</v>
+        <v>0.4474</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.3276</v>
+        <v>-1.3249</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.7955</v>
+        <v>-0.789</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5321</v>
+        <v>-0.5359</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1317,58 +1317,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2468</v>
+        <v>0.2335</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2539</v>
+        <v>-2.2053</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5007</v>
+        <v>2.4388</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0838</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1909</v>
+        <v>-1.2044</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2748</v>
+        <v>1.2832</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1424</v>
+        <v>-0.1506</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6524</v>
+        <v>-0.6588000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>0.51</v>
+        <v>0.5082</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2263</v>
+        <v>0.2293</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5385</v>
+        <v>-0.5457</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7647</v>
+        <v>0.775</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.7019</v>
+        <v>-0.6962</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3397</v>
+        <v>-2.3207</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6378</v>
+        <v>1.6245</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8649</v>
+        <v>0.851</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2282</v>
+        <v>0.266</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6367</v>
+        <v>0.585</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1400,67 +1400,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1309</v>
+        <v>-0.1667</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0458</v>
+        <v>-0.0317</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0852</v>
+        <v>-0.135</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0208</v>
+        <v>0.0237</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6556</v>
+        <v>-0.6616</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6764</v>
+        <v>0.6853</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.717</v>
+        <v>-0.7233000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7902</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0732</v>
+        <v>0.0736</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7378</v>
+        <v>0.7471</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1346</v>
+        <v>0.1353</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6032</v>
+        <v>0.6117</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2104</v>
+        <v>0.1851</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6712</v>
+        <v>0.6916</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4608</v>
+        <v>-0.5065</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1483,67 +1483,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8</v>
+        <v>-3.842</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.2547</v>
+        <v>-3.2264</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5453</v>
+        <v>-0.6157</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.7971</v>
+        <v>-2.8275</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4106</v>
+        <v>-0.4152</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.3865</v>
+        <v>-2.4123</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.1682</v>
+        <v>-2.1944</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2939</v>
+        <v>0.2984</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.4621</v>
+        <v>-2.4928</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6289</v>
+        <v>-0.6331</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7045</v>
+        <v>-0.7136</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0756</v>
+        <v>0.0805</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8272</v>
+        <v>0.8250999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0834</v>
+        <v>0.1284</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7439</v>
+        <v>0.6967</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.5962</v>
+        <v>-1.6076</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.5962</v>
+        <v>-1.6076</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1566,67 +1566,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>32.17000000000001</v>
+        <v>32.1919</v>
       </c>
       <c r="E14" t="n">
-        <v>16.9521</v>
+        <v>17.642</v>
       </c>
       <c r="F14" t="n">
-        <v>15.2176</v>
+        <v>14.5497</v>
       </c>
       <c r="G14" t="n">
-        <v>30.5515</v>
+        <v>30.7816</v>
       </c>
       <c r="H14" t="n">
-        <v>11.4421</v>
+        <v>11.5687</v>
       </c>
       <c r="I14" t="n">
-        <v>19.1092</v>
+        <v>19.2127</v>
       </c>
       <c r="J14" t="n">
-        <v>22.8048</v>
+        <v>22.93429999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>10.3209</v>
+        <v>10.448</v>
       </c>
       <c r="L14" t="n">
-        <v>12.484</v>
+        <v>12.4863</v>
       </c>
       <c r="M14" t="n">
-        <v>7.746700000000001</v>
+        <v>7.847500000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>1.1217</v>
+        <v>1.1205</v>
       </c>
       <c r="O14" t="n">
-        <v>6.624900000000001</v>
+        <v>6.7266</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.498001805406602e-16</v>
+        <v>2.498001805406602e-16</v>
       </c>
       <c r="Q14" t="n">
-        <v>-12.8686</v>
+        <v>-12.7641</v>
       </c>
       <c r="R14" t="n">
-        <v>12.8683</v>
+        <v>12.7638</v>
       </c>
       <c r="S14" t="n">
-        <v>6.406800000000001</v>
+        <v>6.233000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>5.1511</v>
+        <v>5.581300000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2561</v>
+        <v>0.6516000000000002</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.788600000000001</v>
+        <v>-4.822699999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>1.8648</v>
+        <v>1.8903</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.6533</v>
+        <v>-6.712899999999999</v>
       </c>
       <c r="Y14" t="inlineStr"/>
     </row>
@@ -1645,40 +1645,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3409</v>
+        <v>1.3434</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.9797</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3918</v>
+        <v>0.3637</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5523</v>
+        <v>0.5599</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8817</v>
+        <v>0.891</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3294</v>
+        <v>-0.3311</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6177</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.5877</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0366</v>
+        <v>0.0368</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0654</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3006</v>
+        <v>0.3033</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.366</v>
+        <v>-0.3679</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1690,22 +1690,22 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5389</v>
+        <v>-0.5414</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2006</v>
+        <v>-0.1807</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3383</v>
+        <v>-0.3607</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3276</v>
+        <v>1.3249</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5321</v>
+        <v>0.5359</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7955</v>
+        <v>0.789</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1728,58 +1728,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2937</v>
+        <v>-0.2741</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5573</v>
+        <v>-0.5007</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2636</v>
+        <v>0.2266</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4746</v>
+        <v>-0.478</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2145</v>
+        <v>0.2165</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6891</v>
+        <v>-0.6945</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2549</v>
+        <v>0.2584</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0626</v>
+        <v>1.0747</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.8077</v>
+        <v>-0.8164</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7295</v>
+        <v>-0.7364000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8481</v>
+        <v>-0.8583</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1186</v>
+        <v>0.1219</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1809</v>
+        <v>0.2039</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3577</v>
+        <v>0.4013</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1768</v>
+        <v>-0.1974</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1811,64 +1811,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.525</v>
+        <v>-0.4941</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2172</v>
+        <v>0.3084</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7422</v>
+        <v>-0.8025</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1761</v>
+        <v>-0.1687</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0747</v>
+        <v>1.0869</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.2508</v>
+        <v>-1.2555</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4367</v>
+        <v>1.451</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6222</v>
+        <v>1.6419</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1854</v>
+        <v>-0.1909</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6129</v>
+        <v>-1.6196</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5475</v>
+        <v>-0.555</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0654</v>
+        <v>-1.0647</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9359</v>
+        <v>-0.9283</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3397</v>
+        <v>-2.3207</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.6102</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.0349</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5332</v>
+        <v>-0.5753</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1984</v>
+        <v>1.213</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1984</v>
+        <v>1.213</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1894,58 +1894,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3584</v>
+        <v>-1.3526</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0355</v>
+        <v>0.0083</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3228</v>
+        <v>-1.3609</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.0337</v>
+        <v>-2.0507</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7433</v>
+        <v>-1.7632</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2904</v>
+        <v>-0.2874</v>
       </c>
       <c r="J18" t="n">
-        <v>0.083</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.083</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1167</v>
+        <v>-2.1346</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.8263</v>
+        <v>-1.8472</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2904</v>
+        <v>-0.2874</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4945</v>
+        <v>-0.4623</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1186</v>
+        <v>-0.0757</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.376</v>
+        <v>-0.3866</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1977,58 +1977,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9669</v>
+        <v>-1.917</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.519</v>
+        <v>-0.3929</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4479</v>
+        <v>-1.5241</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7551</v>
+        <v>-0.7562</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3127</v>
+        <v>0.3154</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0678</v>
+        <v>-1.0716</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3725</v>
+        <v>2.3929</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0089</v>
+        <v>2.0319</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3636</v>
+        <v>0.361</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.1276</v>
+        <v>-3.1491</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6962</v>
+        <v>-1.7165</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4314</v>
+        <v>-1.4326</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4679</v>
+        <v>-0.4641</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.5737</v>
+        <v>-2.5528</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1057</v>
+        <v>2.0886</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7439</v>
+        <v>-0.6967</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3179</v>
+        <v>-0.233</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.426</v>
+        <v>-0.4637</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2060,64 +2060,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.938</v>
+        <v>-2.9672</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5262</v>
+        <v>-2.4789</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4118</v>
+        <v>-0.4883</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.0956</v>
+        <v>-4.1395</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.12</v>
+        <v>-3.1552</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9756</v>
+        <v>-0.9842</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.7212</v>
+        <v>-2.7566</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.2405</v>
+        <v>-2.2644</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4807</v>
+        <v>-0.4922</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3744</v>
+        <v>-1.3829</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8794999999999999</v>
+        <v>-0.8908</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4949</v>
+        <v>-0.4921</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.4038</v>
+        <v>-1.3924</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9707</v>
+        <v>-0.9712</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5294</v>
+        <v>-0.4733</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4412</v>
+        <v>-0.4978</v>
       </c>
       <c r="V20" t="n">
-        <v>2.1282</v>
+        <v>2.1434</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1282</v>
+        <v>2.1434</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2143,58 +2143,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2769</v>
+        <v>-3.2965</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5361</v>
+        <v>-0.4855</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7408</v>
+        <v>-2.811</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.3548</v>
+        <v>-4.3794</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7677</v>
+        <v>-0.7737000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.5871</v>
+        <v>-3.6057</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9592000000000001</v>
+        <v>-0.9661</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5829</v>
+        <v>0.593</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.5422</v>
+        <v>-1.5592</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.3956</v>
+        <v>-3.4132</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3507</v>
+        <v>-1.3667</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.0449</v>
+        <v>-2.0465</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S21" t="n">
-        <v>0.142</v>
+        <v>0.1546</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6571</v>
+        <v>0.7127</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5151</v>
+        <v>-0.5581</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2226,58 +2226,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6664</v>
+        <v>-3.6574</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1595</v>
+        <v>-3.1114</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5069</v>
+        <v>-0.546</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.523</v>
+        <v>-1.5429</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.9623</v>
+        <v>-1.9844</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4392</v>
+        <v>0.4415</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9031</v>
+        <v>-0.9191</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2667</v>
+        <v>-1.2801</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3636</v>
+        <v>0.361</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6199</v>
+        <v>-0.6238</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6955</v>
+        <v>-0.7043</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0756</v>
+        <v>0.0805</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.6378</v>
+        <v>-1.6245</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3397</v>
+        <v>-2.3207</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5056</v>
+        <v>-0.4901</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0834</v>
+        <v>0.1284</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.589</v>
+        <v>-0.6185</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2309,64 +2309,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8001</v>
+        <v>-3.8294</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6894</v>
+        <v>-1.658</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1107</v>
+        <v>-2.1714</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.2639</v>
+        <v>-5.3028</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7139</v>
+        <v>-0.7221</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.55</v>
+        <v>-4.5808</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.2478</v>
+        <v>-2.2715</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1387</v>
+        <v>0.1408</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.3865</v>
+        <v>-2.4123</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.0161</v>
+        <v>-3.0314</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8526</v>
+        <v>-0.8629</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.1635</v>
+        <v>-2.1684</v>
       </c>
       <c r="P23" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3022</v>
+        <v>-0.2944</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2718</v>
+        <v>-0.2261</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0305</v>
+        <v>-0.0683</v>
       </c>
       <c r="V23" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2392,67 +2392,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.5805</v>
+        <v>-4.6052</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.894</v>
+        <v>-0.8458</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.6865</v>
+        <v>-3.7594</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.5915</v>
+        <v>-2.6015</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7911</v>
+        <v>0.7996</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.3826</v>
+        <v>-3.401</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3966</v>
+        <v>-0.4004</v>
       </c>
       <c r="K24" t="n">
-        <v>1.1456</v>
+        <v>1.1587</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.5422</v>
+        <v>-1.5592</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.1949</v>
+        <v>-2.201</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3545</v>
+        <v>-0.3591</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.8404</v>
+        <v>-1.8419</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7966</v>
+        <v>-0.7886</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4974</v>
+        <v>-0.4454</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2992</v>
+        <v>-0.3433</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.1282</v>
+        <v>-2.1434</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1282</v>
+        <v>-2.1434</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.5085</v>
+        <v>-5.5482</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.139</v>
+        <v>-2.0891</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.3695</v>
+        <v>-3.4592</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.9157</v>
+        <v>-5.9709</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.6741</v>
+        <v>-3.7151</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.2416</v>
+        <v>-2.2559</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.7451</v>
+        <v>-2.7804</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.301</v>
+        <v>-2.3251</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.4441</v>
+        <v>-0.4554</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.1706</v>
+        <v>-3.1905</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.3731</v>
+        <v>-1.39</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.7975</v>
+        <v>-1.8005</v>
       </c>
       <c r="P25" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.429</v>
+        <v>-0.4148</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1738</v>
+        <v>0.2463</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6028</v>
+        <v>-0.6611</v>
       </c>
       <c r="V25" t="n">
-        <v>0.1343</v>
+        <v>0.1413</v>
       </c>
       <c r="W25" t="n">
-        <v>0.6664</v>
+        <v>0.6772</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.5321</v>
+        <v>-0.5359</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2558,64 +2558,64 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.5965</v>
+        <v>-5.5934</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.3281</v>
+        <v>-4.2841</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.2685</v>
+        <v>-1.3093</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.9198</v>
+        <v>-3.9511</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.7358</v>
+        <v>-2.7645</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.184</v>
+        <v>-1.1865</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.5384</v>
+        <v>-2.564</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.5384</v>
+        <v>-2.564</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.3814</v>
+        <v>-1.3871</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.1975</v>
+        <v>-0.2005</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.184</v>
+        <v>-1.1865</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.4038</v>
+        <v>-1.3924</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.3397</v>
+        <v>-2.3207</v>
       </c>
       <c r="R26" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.337</v>
+        <v>-1.3216</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5141</v>
+        <v>-0.471</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.8229</v>
+        <v>-0.8505</v>
       </c>
       <c r="V26" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="W26" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -2641,67 +2641,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-32.17</v>
+        <v>-32.1917</v>
       </c>
       <c r="E27" t="n">
-        <v>-15.2178</v>
+        <v>-14.55</v>
       </c>
       <c r="F27" t="n">
-        <v>-16.9522</v>
+        <v>-17.6418</v>
       </c>
       <c r="G27" t="n">
-        <v>-30.5515</v>
+        <v>-30.7818</v>
       </c>
       <c r="H27" t="n">
-        <v>-11.4424</v>
+        <v>-11.5688</v>
       </c>
       <c r="I27" t="n">
-        <v>-19.1092</v>
+        <v>-19.2127</v>
       </c>
       <c r="J27" t="n">
-        <v>-7.7466</v>
+        <v>-7.8473</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.1216</v>
+        <v>-1.1209</v>
       </c>
       <c r="L27" t="n">
-        <v>-6.625</v>
+        <v>-6.7268</v>
       </c>
       <c r="M27" t="n">
-        <v>-22.805</v>
+        <v>-22.9343</v>
       </c>
       <c r="N27" t="n">
-        <v>-10.3209</v>
+        <v>-10.448</v>
       </c>
       <c r="O27" t="n">
-        <v>-12.4842</v>
+        <v>-12.4861</v>
       </c>
       <c r="P27" t="n">
         <v>9.999999999998899e-05</v>
       </c>
       <c r="Q27" t="n">
-        <v>-12.8685</v>
+        <v>-12.764</v>
       </c>
       <c r="R27" t="n">
-        <v>12.8685</v>
+        <v>12.764</v>
       </c>
       <c r="S27" t="n">
-        <v>-6.4069</v>
+        <v>-6.2328</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.256</v>
+        <v>-0.6514000000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>-5.151</v>
+        <v>-5.581300000000001</v>
       </c>
       <c r="V27" t="n">
-        <v>4.788499999999999</v>
+        <v>4.8226</v>
       </c>
       <c r="W27" t="n">
-        <v>6.6533</v>
+        <v>6.7129</v>
       </c>
       <c r="X27" t="n">
-        <v>-1.8648</v>
+        <v>-1.8903</v>
       </c>
       <c r="Y27" t="inlineStr"/>
     </row>
